--- a/data/nzd0536/nzd0536.xlsx
+++ b/data/nzd0536/nzd0536.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G488"/>
+  <dimension ref="A1:G489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13614,6 +13614,33 @@
       <c r="G488" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>329.46</v>
+      </c>
+      <c r="C489" t="n">
+        <v>323.84</v>
+      </c>
+      <c r="D489" t="n">
+        <v>313.69</v>
+      </c>
+      <c r="E489" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="F489" t="n">
+        <v>319.96</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13628,7 +13655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B566"/>
+  <dimension ref="A1:B567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19291,6 +19318,16 @@
       </c>
       <c r="B566" t="n">
         <v>0.45</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -19459,28 +19496,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09207202316802879</v>
+        <v>0.09182724785682345</v>
       </c>
       <c r="J2" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K2" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0373087716568764</v>
+        <v>0.03727661241048419</v>
       </c>
       <c r="M2" t="n">
-        <v>2.720847081493883</v>
+        <v>2.716582813598932</v>
       </c>
       <c r="N2" t="n">
-        <v>12.53472079731353</v>
+        <v>12.50979979078576</v>
       </c>
       <c r="O2" t="n">
-        <v>3.540440763141438</v>
+        <v>3.536919534112383</v>
       </c>
       <c r="P2" t="n">
-        <v>327.642454729966</v>
+        <v>327.6449128656666</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19537,28 +19574,28 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07387059681474982</v>
+        <v>0.07405530168031738</v>
       </c>
       <c r="J3" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K3" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01882263246170435</v>
+        <v>0.01899808960986271</v>
       </c>
       <c r="M3" t="n">
-        <v>3.067922721026081</v>
+        <v>3.062510848709104</v>
       </c>
       <c r="N3" t="n">
-        <v>16.30022515940711</v>
+        <v>16.26725859487512</v>
       </c>
       <c r="O3" t="n">
-        <v>4.037353732261654</v>
+        <v>4.033268971302946</v>
       </c>
       <c r="P3" t="n">
-        <v>321.4305387856591</v>
+        <v>321.4286839024118</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19615,28 +19652,28 @@
         <v>0.1285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07874469090520138</v>
+        <v>0.07872770527546082</v>
       </c>
       <c r="J4" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K4" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03317276675560121</v>
+        <v>0.03330315349064505</v>
       </c>
       <c r="M4" t="n">
-        <v>2.570665998348799</v>
+        <v>2.565495084569751</v>
       </c>
       <c r="N4" t="n">
-        <v>10.35602220941337</v>
+        <v>10.3348045356743</v>
       </c>
       <c r="O4" t="n">
-        <v>3.218077408859732</v>
+        <v>3.214779080383954</v>
       </c>
       <c r="P4" t="n">
-        <v>311.6607213980809</v>
+        <v>311.6608919748545</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19693,28 +19730,28 @@
         <v>0.1609</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.001314818357993349</v>
+        <v>-0.001157696229135253</v>
       </c>
       <c r="J5" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K5" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L5" t="n">
-        <v>8.515506714434906e-06</v>
+        <v>6.631427317826954e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>2.603345646468175</v>
+        <v>2.598636176387719</v>
       </c>
       <c r="N5" t="n">
-        <v>11.63323637409852</v>
+        <v>11.6097129431048</v>
       </c>
       <c r="O5" t="n">
-        <v>3.410753050881656</v>
+        <v>3.407302883969196</v>
       </c>
       <c r="P5" t="n">
-        <v>315.5381318091983</v>
+        <v>315.5365539232898</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19771,28 +19808,28 @@
         <v>0.1333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01281403736740284</v>
+        <v>0.01227928432621635</v>
       </c>
       <c r="J6" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K6" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005925407697546792</v>
+        <v>0.0005464646490077607</v>
       </c>
       <c r="M6" t="n">
-        <v>2.948462136704326</v>
+        <v>2.944880549490052</v>
       </c>
       <c r="N6" t="n">
-        <v>15.87009584154682</v>
+        <v>15.84122583628819</v>
       </c>
       <c r="O6" t="n">
-        <v>3.983728886551746</v>
+        <v>3.980103746925222</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9589218649593</v>
+        <v>320.9642920778908</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19830,7 +19867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G488"/>
+  <dimension ref="A1:G489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37889,6 +37926,43 @@
         </is>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>-46.38397807381591,168.01547524704236</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-46.383782051226675,168.01462319854915</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>-46.38354696187065,168.0137876201853</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-46.383418464702906,168.01290710642218</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>-46.38330592130381,168.0120198661339</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0536/nzd0536.xlsx
+++ b/data/nzd0536/nzd0536.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G489"/>
+  <dimension ref="A1:G491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13639,6 +13639,60 @@
         <v>319.96</v>
       </c>
       <c r="G489" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>329.14</v>
+      </c>
+      <c r="C490" t="n">
+        <v>323.85</v>
+      </c>
+      <c r="D490" t="n">
+        <v>313.82</v>
+      </c>
+      <c r="E490" t="n">
+        <v>315.62</v>
+      </c>
+      <c r="F490" t="n">
+        <v>319.45</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>330.05</v>
+      </c>
+      <c r="C491" t="n">
+        <v>324.91</v>
+      </c>
+      <c r="D491" t="n">
+        <v>314.79</v>
+      </c>
+      <c r="E491" t="n">
+        <v>317.66</v>
+      </c>
+      <c r="F491" t="n">
+        <v>321.01</v>
+      </c>
+      <c r="G491" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13655,7 +13709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B567"/>
+  <dimension ref="A1:B569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19328,6 +19382,26 @@
       </c>
       <c r="B567" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -19496,28 +19570,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09182724785682345</v>
+        <v>0.09145419791427303</v>
       </c>
       <c r="J2" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K2" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03727661241048419</v>
+        <v>0.03729941486372468</v>
       </c>
       <c r="M2" t="n">
-        <v>2.716582813598932</v>
+        <v>2.707481017241919</v>
       </c>
       <c r="N2" t="n">
-        <v>12.50979979078576</v>
+        <v>12.46048043813284</v>
       </c>
       <c r="O2" t="n">
-        <v>3.536919534112383</v>
+        <v>3.529940571473242</v>
       </c>
       <c r="P2" t="n">
-        <v>327.6449128656666</v>
+        <v>327.6486629743054</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19574,28 +19648,28 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07405530168031738</v>
+        <v>0.07484170216663147</v>
       </c>
       <c r="J3" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K3" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01899808960986271</v>
+        <v>0.01956009105800893</v>
       </c>
       <c r="M3" t="n">
-        <v>3.062510848709104</v>
+        <v>3.053707837442108</v>
       </c>
       <c r="N3" t="n">
-        <v>16.26725859487512</v>
+        <v>16.20599504713103</v>
       </c>
       <c r="O3" t="n">
-        <v>4.033268971302946</v>
+        <v>4.025667031329221</v>
       </c>
       <c r="P3" t="n">
-        <v>321.4286839024118</v>
+        <v>321.4207726082487</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19652,28 +19726,28 @@
         <v>0.1285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07872770527546082</v>
+        <v>0.07917571400454983</v>
       </c>
       <c r="J4" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K4" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03330315349064505</v>
+        <v>0.03395466965575389</v>
       </c>
       <c r="M4" t="n">
-        <v>2.565495084569751</v>
+        <v>2.557050537055031</v>
       </c>
       <c r="N4" t="n">
-        <v>10.3348045356743</v>
+        <v>10.29485545884472</v>
       </c>
       <c r="O4" t="n">
-        <v>3.214779080383954</v>
+        <v>3.208559717200963</v>
       </c>
       <c r="P4" t="n">
-        <v>311.6608919748545</v>
+        <v>311.6563842360678</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19730,28 +19804,28 @@
         <v>0.1609</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.001157696229135253</v>
+        <v>-0.0002605716244927887</v>
       </c>
       <c r="J5" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K5" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L5" t="n">
-        <v>6.631427317826954e-06</v>
+        <v>3.386830147444897e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.598636176387719</v>
+        <v>2.591568200308609</v>
       </c>
       <c r="N5" t="n">
-        <v>11.6097129431048</v>
+        <v>11.57174774757255</v>
       </c>
       <c r="O5" t="n">
-        <v>3.407302883969196</v>
+        <v>3.401727171242948</v>
       </c>
       <c r="P5" t="n">
-        <v>315.5365539232898</v>
+        <v>315.527527076306</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19808,28 +19882,28 @@
         <v>0.1333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01227928432621635</v>
+        <v>0.01144355794898878</v>
       </c>
       <c r="J6" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K6" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005464646490077607</v>
+        <v>0.0004786819764227568</v>
       </c>
       <c r="M6" t="n">
-        <v>2.944880549490052</v>
+        <v>2.936686953802645</v>
       </c>
       <c r="N6" t="n">
-        <v>15.84122583628819</v>
+        <v>15.78357624600466</v>
       </c>
       <c r="O6" t="n">
-        <v>3.980103746925222</v>
+        <v>3.972854923855722</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9642920778908</v>
+        <v>320.9726942109567</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19867,7 +19941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G489"/>
+  <dimension ref="A1:G491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37963,6 +38037,80 @@
         </is>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>-46.38397531412746,168.01547641038795</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-46.3837821374667,168.01462316219386</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-46.38354808298819,168.0137871475578</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-46.383416049995034,168.0129081244124</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>-46.38330152309848,168.01202172037395</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-46.38398316199143,168.01547310212362</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-46.38379127891013,168.01461930853284</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-46.38355644824967,168.01378362102858</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-46.38343364286637,168.01290070762414</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>-46.38331497643227,168.01201604857977</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0536/nzd0536.xlsx
+++ b/data/nzd0536/nzd0536.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G491"/>
+  <dimension ref="A1:G492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13693,6 +13693,33 @@
         <v>321.01</v>
       </c>
       <c r="G491" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:27:11+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>330.43</v>
+      </c>
+      <c r="C492" t="n">
+        <v>325.35</v>
+      </c>
+      <c r="D492" t="n">
+        <v>315.27</v>
+      </c>
+      <c r="E492" t="n">
+        <v>318.03</v>
+      </c>
+      <c r="F492" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="G492" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13709,7 +13736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B569"/>
+  <dimension ref="A1:B570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19402,6 +19429,16 @@
       </c>
       <c r="B569" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -19570,28 +19607,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09145419791427303</v>
+        <v>0.09159701509819886</v>
       </c>
       <c r="J2" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K2" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03729941486372468</v>
+        <v>0.03757126286758117</v>
       </c>
       <c r="M2" t="n">
-        <v>2.707481017241919</v>
+        <v>2.7026767330873</v>
       </c>
       <c r="N2" t="n">
-        <v>12.46048043813284</v>
+        <v>12.43536760797192</v>
       </c>
       <c r="O2" t="n">
-        <v>3.529940571473242</v>
+        <v>3.526381659431084</v>
       </c>
       <c r="P2" t="n">
-        <v>327.6486629743054</v>
+        <v>327.6472230071049</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19648,28 +19685,28 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07484170216663147</v>
+        <v>0.07560954165853695</v>
       </c>
       <c r="J3" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K3" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01956009105800893</v>
+        <v>0.02003327064194105</v>
       </c>
       <c r="M3" t="n">
-        <v>3.053707837442108</v>
+        <v>3.051079913428863</v>
       </c>
       <c r="N3" t="n">
-        <v>16.20599504713103</v>
+        <v>16.18064688379367</v>
       </c>
       <c r="O3" t="n">
-        <v>4.025667031329221</v>
+        <v>4.022517480856195</v>
       </c>
       <c r="P3" t="n">
-        <v>321.4207726082487</v>
+        <v>321.413030796982</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19726,28 +19763,28 @@
         <v>0.1285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07917571400454983</v>
+        <v>0.07977676190101018</v>
       </c>
       <c r="J4" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K4" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03395466965575389</v>
+        <v>0.03458723874278125</v>
       </c>
       <c r="M4" t="n">
-        <v>2.557050537055031</v>
+        <v>2.554544281183396</v>
       </c>
       <c r="N4" t="n">
-        <v>10.29485545884472</v>
+        <v>10.2785806750702</v>
       </c>
       <c r="O4" t="n">
-        <v>3.208559717200963</v>
+        <v>3.206022563094371</v>
       </c>
       <c r="P4" t="n">
-        <v>311.6563842360678</v>
+        <v>311.6503241161785</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19804,28 +19841,28 @@
         <v>0.1609</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0002605716244927887</v>
+        <v>0.0007281811036440344</v>
       </c>
       <c r="J5" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K5" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L5" t="n">
-        <v>3.386830147444897e-07</v>
+        <v>2.653811196129396e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>2.591568200308609</v>
+        <v>2.590162815632355</v>
       </c>
       <c r="N5" t="n">
-        <v>11.57174774757255</v>
+        <v>11.5608783531009</v>
       </c>
       <c r="O5" t="n">
-        <v>3.401727171242948</v>
+        <v>3.400129167120112</v>
       </c>
       <c r="P5" t="n">
-        <v>315.527527076306</v>
+        <v>315.5175578873136</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19882,28 +19919,28 @@
         <v>0.1333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01144355794898878</v>
+        <v>0.01141293478057805</v>
       </c>
       <c r="J6" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K6" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004786819764227568</v>
+        <v>0.000478244277903106</v>
       </c>
       <c r="M6" t="n">
-        <v>2.936686953802645</v>
+        <v>2.930844976932321</v>
       </c>
       <c r="N6" t="n">
-        <v>15.78357624600466</v>
+        <v>15.75144265020458</v>
       </c>
       <c r="O6" t="n">
-        <v>3.972854923855722</v>
+        <v>3.968808719276425</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9726942109567</v>
+        <v>320.9730029718276</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19941,7 +19978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G491"/>
+  <dimension ref="A1:G492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38111,6 +38148,43 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:27:11+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>-46.383986439121415,168.01547172065028</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>-46.38379507347149,168.01461770889955</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>-46.38356058776048,168.0137818759415</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-46.38343683373021,168.0128993624218</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>-46.38331661497931,168.01201535778412</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0536/nzd0536.xlsx
+++ b/data/nzd0536/nzd0536.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G492"/>
+  <dimension ref="A1:G493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13722,6 +13722,33 @@
       <c r="G492" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>330.56</v>
+      </c>
+      <c r="C493" t="n">
+        <v>327.31</v>
+      </c>
+      <c r="D493" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="E493" t="n">
+        <v>317.86</v>
+      </c>
+      <c r="F493" t="n">
+        <v>319.6</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B570"/>
+  <dimension ref="A1:B571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19439,6 +19466,16 @@
       </c>
       <c r="B570" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -19607,28 +19644,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09159701509819886</v>
+        <v>0.09178679372588913</v>
       </c>
       <c r="J2" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K2" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03757126286758117</v>
+        <v>0.03788459068050043</v>
       </c>
       <c r="M2" t="n">
-        <v>2.7026767330873</v>
+        <v>2.698112327649451</v>
       </c>
       <c r="N2" t="n">
-        <v>12.43536760797192</v>
+        <v>12.41055278217868</v>
       </c>
       <c r="O2" t="n">
-        <v>3.526381659431084</v>
+        <v>3.522861448053086</v>
       </c>
       <c r="P2" t="n">
-        <v>327.6472230071049</v>
+        <v>327.6452963379169</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19685,28 +19722,28 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07560954165853695</v>
+        <v>0.07715575780620533</v>
       </c>
       <c r="J3" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K3" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02003327064194105</v>
+        <v>0.02089765848646707</v>
       </c>
       <c r="M3" t="n">
-        <v>3.051079913428863</v>
+        <v>3.051998877946576</v>
       </c>
       <c r="N3" t="n">
-        <v>16.18064688379367</v>
+        <v>16.17831547760277</v>
       </c>
       <c r="O3" t="n">
-        <v>4.022517480856195</v>
+        <v>4.022227676002785</v>
       </c>
       <c r="P3" t="n">
-        <v>321.413030796982</v>
+        <v>321.3973333127818</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19763,28 +19800,28 @@
         <v>0.1285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07977676190101018</v>
+        <v>0.08076126947946381</v>
       </c>
       <c r="J4" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K4" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03458723874278125</v>
+        <v>0.03552938789760518</v>
       </c>
       <c r="M4" t="n">
-        <v>2.554544281183396</v>
+        <v>2.553723932302868</v>
       </c>
       <c r="N4" t="n">
-        <v>10.2785806750702</v>
+        <v>10.27007708738137</v>
       </c>
       <c r="O4" t="n">
-        <v>3.206022563094371</v>
+        <v>3.204696099067955</v>
       </c>
       <c r="P4" t="n">
-        <v>311.6503241161785</v>
+        <v>311.6403292055826</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19841,28 +19878,28 @@
         <v>0.1609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0007281811036440344</v>
+        <v>0.001649960007815925</v>
       </c>
       <c r="J5" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K5" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L5" t="n">
-        <v>2.653811196129396e-06</v>
+        <v>1.36738636853373e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.590162815632355</v>
+        <v>2.588440325194824</v>
       </c>
       <c r="N5" t="n">
-        <v>11.5608783531009</v>
+        <v>11.54824015876082</v>
       </c>
       <c r="O5" t="n">
-        <v>3.400129167120112</v>
+        <v>3.398270171537399</v>
       </c>
       <c r="P5" t="n">
-        <v>315.5175578873136</v>
+        <v>315.5081998103034</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19919,28 +19956,28 @@
         <v>0.1333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01141293478057805</v>
+        <v>0.01074767823496959</v>
       </c>
       <c r="J6" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K6" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000478244277903106</v>
+        <v>0.0004259096577802213</v>
       </c>
       <c r="M6" t="n">
-        <v>2.930844976932321</v>
+        <v>2.927857500226744</v>
       </c>
       <c r="N6" t="n">
-        <v>15.75144265020458</v>
+        <v>15.72508386471191</v>
       </c>
       <c r="O6" t="n">
-        <v>3.968808719276425</v>
+        <v>3.965486586121798</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9730029718276</v>
+        <v>320.9797567844362</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19978,7 +20015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G492"/>
+  <dimension ref="A1:G493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38185,6 +38222,43 @@
         </is>
       </c>
     </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>-46.38398756024482,168.01547124804097</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>-46.38381197651719,168.01461058325742</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-46.38356903926155,168.01377831305456</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-46.38343536765764,168.01289998048776</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>-46.38330281668829,168.01202117500927</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0536/nzd0536.xlsx
+++ b/data/nzd0536/nzd0536.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G493"/>
+  <dimension ref="A1:G494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13749,6 +13749,33 @@
       <c r="G493" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>332.46</v>
+      </c>
+      <c r="C494" t="n">
+        <v>328.22</v>
+      </c>
+      <c r="D494" t="n">
+        <v>317.32</v>
+      </c>
+      <c r="E494" t="n">
+        <v>318.62</v>
+      </c>
+      <c r="F494" t="n">
+        <v>321.1</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13763,7 +13790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B571"/>
+  <dimension ref="A1:B572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19476,6 +19503,16 @@
       </c>
       <c r="B571" t="n">
         <v>-0.75</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -19644,28 +19681,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09178679372588913</v>
+        <v>0.09272501007020519</v>
       </c>
       <c r="J2" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K2" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03788459068050043</v>
+        <v>0.03876660716186875</v>
       </c>
       <c r="M2" t="n">
-        <v>2.698112327649451</v>
+        <v>2.697222836417517</v>
       </c>
       <c r="N2" t="n">
-        <v>12.41055278217868</v>
+        <v>12.39671095276069</v>
       </c>
       <c r="O2" t="n">
-        <v>3.522861448053086</v>
+        <v>3.520896328033628</v>
       </c>
       <c r="P2" t="n">
-        <v>327.6452963379169</v>
+        <v>327.6357621391167</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19722,28 +19759,28 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07715575780620533</v>
+        <v>0.07904061015663841</v>
       </c>
       <c r="J3" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K3" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02089765848646707</v>
+        <v>0.02194450351545618</v>
       </c>
       <c r="M3" t="n">
-        <v>3.051998877946576</v>
+        <v>3.0544725670594</v>
       </c>
       <c r="N3" t="n">
-        <v>16.17831547760277</v>
+        <v>16.19123392515089</v>
       </c>
       <c r="O3" t="n">
-        <v>4.022227676002785</v>
+        <v>4.023833237741208</v>
       </c>
       <c r="P3" t="n">
-        <v>321.3973333127818</v>
+        <v>321.3781793541806</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19800,28 +19837,28 @@
         <v>0.1285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08076126947946381</v>
+        <v>0.08215669571449542</v>
       </c>
       <c r="J4" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K4" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03552938789760518</v>
+        <v>0.03679538565622464</v>
       </c>
       <c r="M4" t="n">
-        <v>2.553723932302868</v>
+        <v>2.554919227386872</v>
       </c>
       <c r="N4" t="n">
-        <v>10.27007708738137</v>
+        <v>10.27431232854357</v>
       </c>
       <c r="O4" t="n">
-        <v>3.204696099067955</v>
+        <v>3.205356817663763</v>
       </c>
       <c r="P4" t="n">
-        <v>311.6403292055826</v>
+        <v>311.6261488182804</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19878,28 +19915,28 @@
         <v>0.1609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001649960007815925</v>
+        <v>0.002864553364002429</v>
       </c>
       <c r="J5" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K5" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36738636853373e-05</v>
+        <v>4.133219517699072e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.588440325194824</v>
+        <v>2.587836359567105</v>
       </c>
       <c r="N5" t="n">
-        <v>11.54824015876082</v>
+        <v>11.54380687927435</v>
       </c>
       <c r="O5" t="n">
-        <v>3.398270171537399</v>
+        <v>3.397617824193055</v>
       </c>
       <c r="P5" t="n">
-        <v>315.5081998103034</v>
+        <v>315.4958570552562</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19956,28 +19993,28 @@
         <v>0.1333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01074767823496959</v>
+        <v>0.01068319541872076</v>
       </c>
       <c r="J6" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K6" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004259096577802213</v>
+        <v>0.0004227150682669656</v>
       </c>
       <c r="M6" t="n">
-        <v>2.927857500226744</v>
+        <v>2.922205272513809</v>
       </c>
       <c r="N6" t="n">
-        <v>15.72508386471191</v>
+        <v>15.69324067041736</v>
       </c>
       <c r="O6" t="n">
-        <v>3.965486586121798</v>
+        <v>3.961469508959694</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9797567844362</v>
+        <v>320.9804120618602</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20015,7 +20052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G493"/>
+  <dimension ref="A1:G494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38259,6 +38296,43 @@
         </is>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>-46.384003945894285,168.01546434067131</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>-46.38381982435961,168.01460727492193</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-46.383578266920715,168.01377442296229</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-46.383441921864396,168.01289721736902</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-46.38331575258613,168.01201572136077</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0536/nzd0536.xlsx
+++ b/data/nzd0536/nzd0536.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G494"/>
+  <dimension ref="A1:G495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13774,6 +13774,33 @@
         <v>321.1</v>
       </c>
       <c r="G494" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>332.9</v>
+      </c>
+      <c r="C495" t="n">
+        <v>329</v>
+      </c>
+      <c r="D495" t="n">
+        <v>318.33</v>
+      </c>
+      <c r="E495" t="n">
+        <v>319.58</v>
+      </c>
+      <c r="F495" t="n">
+        <v>321.79</v>
+      </c>
+      <c r="G495" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13790,7 +13817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B572"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19513,6 +19540,16 @@
       </c>
       <c r="B572" t="n">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -19681,28 +19718,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09272501007020519</v>
+        <v>0.09382782575106176</v>
       </c>
       <c r="J2" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K2" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03876660716186875</v>
+        <v>0.03978078991935519</v>
       </c>
       <c r="M2" t="n">
-        <v>2.697222836417517</v>
+        <v>2.697129450904836</v>
       </c>
       <c r="N2" t="n">
-        <v>12.39671095276069</v>
+        <v>12.38732515075912</v>
       </c>
       <c r="O2" t="n">
-        <v>3.520896328033628</v>
+        <v>3.519563204541029</v>
       </c>
       <c r="P2" t="n">
-        <v>327.6357621391167</v>
+        <v>327.6245335221217</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19759,28 +19796,28 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07904061015663841</v>
+        <v>0.08121538550680846</v>
       </c>
       <c r="J3" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K3" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02194450351545618</v>
+        <v>0.02315687535894873</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0544725670594</v>
+        <v>3.058495400798717</v>
       </c>
       <c r="N3" t="n">
-        <v>16.19123392515089</v>
+        <v>16.21954738389572</v>
       </c>
       <c r="O3" t="n">
-        <v>4.023833237741208</v>
+        <v>4.027349920716565</v>
       </c>
       <c r="P3" t="n">
-        <v>321.3781793541806</v>
+        <v>321.3560362890418</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19837,28 +19874,28 @@
         <v>0.1285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08215669571449542</v>
+        <v>0.08393841941550889</v>
       </c>
       <c r="J4" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K4" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03679538565622464</v>
+        <v>0.03836567055324669</v>
       </c>
       <c r="M4" t="n">
-        <v>2.554919227386872</v>
+        <v>2.557917876177012</v>
       </c>
       <c r="N4" t="n">
-        <v>10.27431232854357</v>
+        <v>10.29451721707976</v>
       </c>
       <c r="O4" t="n">
-        <v>3.205356817663763</v>
+        <v>3.208507007484908</v>
       </c>
       <c r="P4" t="n">
-        <v>311.6261488182804</v>
+        <v>311.6080077151232</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19915,28 +19952,28 @@
         <v>0.1609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002864553364002429</v>
+        <v>0.004447559466332194</v>
       </c>
       <c r="J5" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K5" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L5" t="n">
-        <v>4.133219517699072e-05</v>
+        <v>9.979986548247499e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.587836359567105</v>
+        <v>2.588657149768789</v>
       </c>
       <c r="N5" t="n">
-        <v>11.54380687927435</v>
+        <v>11.55280574628165</v>
       </c>
       <c r="O5" t="n">
-        <v>3.397617824193055</v>
+        <v>3.398941856855108</v>
       </c>
       <c r="P5" t="n">
-        <v>315.4958570552562</v>
+        <v>315.4797392492325</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19993,28 +20030,28 @@
         <v>0.1333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01068319541872076</v>
+        <v>0.01089020547174501</v>
       </c>
       <c r="J6" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K6" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004227150682669656</v>
+        <v>0.0004412145026252423</v>
       </c>
       <c r="M6" t="n">
-        <v>2.922205272513809</v>
+        <v>2.917485655377854</v>
       </c>
       <c r="N6" t="n">
-        <v>15.69324067041736</v>
+        <v>15.66202647820218</v>
       </c>
       <c r="O6" t="n">
-        <v>3.961469508959694</v>
+        <v>3.957527824059128</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9804120618602</v>
+        <v>320.9783043328536</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20052,7 +20089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G494"/>
+  <dimension ref="A1:G495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38333,6 +38370,43 @@
         </is>
       </c>
     </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>-46.384007740465634,168.01546274106929</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>-46.38382655108157,168.014604439205</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-46.383586977140844,168.01377075100473</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-46.383450200862285,168.01289372711275</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>-46.38332170309901,168.01201321268152</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0536/nzd0536.xlsx
+++ b/data/nzd0536/nzd0536.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G495"/>
+  <dimension ref="A1:G499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13803,6 +13803,114 @@
       <c r="G495" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>332.06</v>
+      </c>
+      <c r="C496" t="n">
+        <v>328.59</v>
+      </c>
+      <c r="D496" t="n">
+        <v>318.46</v>
+      </c>
+      <c r="E496" t="n">
+        <v>317.89</v>
+      </c>
+      <c r="F496" t="n">
+        <v>320.49</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>332.1</v>
+      </c>
+      <c r="C497" t="n">
+        <v>328.94</v>
+      </c>
+      <c r="D497" t="n">
+        <v>318.29</v>
+      </c>
+      <c r="E497" t="n">
+        <v>318.18</v>
+      </c>
+      <c r="F497" t="n">
+        <v>321.23</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>332.76</v>
+      </c>
+      <c r="C498" t="n">
+        <v>329.3</v>
+      </c>
+      <c r="D498" t="n">
+        <v>319.25</v>
+      </c>
+      <c r="E498" t="n">
+        <v>318.77</v>
+      </c>
+      <c r="F498" t="n">
+        <v>321.19</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>332.22</v>
+      </c>
+      <c r="C499" t="n">
+        <v>328.51</v>
+      </c>
+      <c r="D499" t="n">
+        <v>319.76</v>
+      </c>
+      <c r="E499" t="n">
+        <v>318.78</v>
+      </c>
+      <c r="F499" t="n">
+        <v>322.07</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19550,6 +19658,46 @@
       </c>
       <c r="B573" t="n">
         <v>0.12</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -19718,28 +19866,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09382782575106176</v>
+        <v>0.09716596218930711</v>
       </c>
       <c r="J2" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="K2" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03978078991935519</v>
+        <v>0.04315963884943907</v>
       </c>
       <c r="M2" t="n">
-        <v>2.697129450904836</v>
+        <v>2.691594783177285</v>
       </c>
       <c r="N2" t="n">
-        <v>12.38732515075912</v>
+        <v>12.32438057496628</v>
       </c>
       <c r="O2" t="n">
-        <v>3.519563204541029</v>
+        <v>3.510609715557439</v>
       </c>
       <c r="P2" t="n">
-        <v>327.6245335221217</v>
+        <v>327.5903208776757</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19796,28 +19944,28 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08121538550680846</v>
+        <v>0.08947162825413414</v>
       </c>
       <c r="J3" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="K3" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02315687535894873</v>
+        <v>0.02808819808191088</v>
       </c>
       <c r="M3" t="n">
-        <v>3.058495400798717</v>
+        <v>3.073690492560934</v>
       </c>
       <c r="N3" t="n">
-        <v>16.21954738389572</v>
+        <v>16.30980481254987</v>
       </c>
       <c r="O3" t="n">
-        <v>4.027349920716565</v>
+        <v>4.038539935737899</v>
       </c>
       <c r="P3" t="n">
-        <v>321.3560362890418</v>
+        <v>321.2714211344117</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19874,28 +20022,28 @@
         <v>0.1285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08393841941550889</v>
+        <v>0.09185344915345538</v>
       </c>
       <c r="J4" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="K4" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03836567055324669</v>
+        <v>0.04552053555295144</v>
       </c>
       <c r="M4" t="n">
-        <v>2.557917876177012</v>
+        <v>2.574150266063291</v>
       </c>
       <c r="N4" t="n">
-        <v>10.29451721707976</v>
+        <v>10.41658277181004</v>
       </c>
       <c r="O4" t="n">
-        <v>3.208507007484908</v>
+        <v>3.227473124878043</v>
       </c>
       <c r="P4" t="n">
-        <v>311.6080077151232</v>
+        <v>311.5268828696301</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19952,28 +20100,28 @@
         <v>0.1609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004447559466332194</v>
+        <v>0.008819856992375549</v>
       </c>
       <c r="J5" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="K5" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="L5" t="n">
-        <v>9.979986548247499e-05</v>
+        <v>0.0003973453273249383</v>
       </c>
       <c r="M5" t="n">
-        <v>2.588657149768789</v>
+        <v>2.584618354235614</v>
       </c>
       <c r="N5" t="n">
-        <v>11.55280574628165</v>
+        <v>11.52278563701998</v>
       </c>
       <c r="O5" t="n">
-        <v>3.398941856855108</v>
+        <v>3.394522887979985</v>
       </c>
       <c r="P5" t="n">
-        <v>315.4797392492325</v>
+        <v>315.4349239798231</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20030,28 +20178,28 @@
         <v>0.1333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01089020547174501</v>
+        <v>0.01085660293649419</v>
       </c>
       <c r="J6" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="K6" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004412145026252423</v>
+        <v>0.0004464295794311957</v>
       </c>
       <c r="M6" t="n">
-        <v>2.917485655377854</v>
+        <v>2.897438446734103</v>
       </c>
       <c r="N6" t="n">
-        <v>15.66202647820218</v>
+        <v>15.53875168716341</v>
       </c>
       <c r="O6" t="n">
-        <v>3.957527824059128</v>
+        <v>3.941922333984196</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9783043328536</v>
+        <v>320.978639713535</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20089,7 +20237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G495"/>
+  <dimension ref="A1:G499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38407,6 +38555,154 @@
         </is>
       </c>
     </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>-46.38400049628391,168.01546579485478</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-46.38382301524056,168.01460592977423</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-46.38358809825827,168.01377027837646</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-46.383435626376325,168.0128998714173</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>-46.383310491987714,168.01201793917818</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-46.38400084124494,168.01546564943644</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-46.383826033641434,168.0146046573371</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-46.38358663218164,168.01377089642884</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-46.38343812732365,168.0128988170694</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-46.383316873697254,168.01201524871112</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-46.38400653310203,168.01546325003358</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-46.38382913828231,168.0146033485444</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-46.38359491120262,168.0137674062502</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-46.38344321545782,168.01289667201655</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-46.383316528739996,168.01201539414177</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-46.38400187612807,168.01546521318141</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-46.383822325320345,168.014606220617</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-46.38359930943244,168.01376555209237</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-46.38344330169739,168.0128966356597</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-46.38332411779987,168.01201219466662</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0536/nzd0536.xlsx
+++ b/data/nzd0536/nzd0536.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G499"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13909,6 +13909,33 @@
         <v>322.07</v>
       </c>
       <c r="G499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>332.11</v>
+      </c>
+      <c r="C500" t="n">
+        <v>327.83</v>
+      </c>
+      <c r="D500" t="n">
+        <v>319.12</v>
+      </c>
+      <c r="E500" t="n">
+        <v>318.07</v>
+      </c>
+      <c r="F500" t="n">
+        <v>322.69</v>
+      </c>
+      <c r="G500" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13925,7 +13952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B577"/>
+  <dimension ref="A1:B578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19698,6 +19725,16 @@
       </c>
       <c r="B577" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -19866,28 +19903,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09716596218930711</v>
+        <v>0.09790850536566592</v>
       </c>
       <c r="J2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04315963884943907</v>
+        <v>0.04395789583063614</v>
       </c>
       <c r="M2" t="n">
-        <v>2.691594783177285</v>
+        <v>2.689832811821501</v>
       </c>
       <c r="N2" t="n">
-        <v>12.32438057496628</v>
+        <v>12.30686803278006</v>
       </c>
       <c r="O2" t="n">
-        <v>3.510609715557439</v>
+        <v>3.508114598011311</v>
       </c>
       <c r="P2" t="n">
-        <v>327.5903208776757</v>
+        <v>327.5826724892993</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19944,28 +19981,28 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08947162825413414</v>
+        <v>0.09109168501646896</v>
       </c>
       <c r="J3" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K3" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02808819808191088</v>
+        <v>0.02915315456180201</v>
       </c>
       <c r="M3" t="n">
-        <v>3.073690492560934</v>
+        <v>3.075357009318052</v>
       </c>
       <c r="N3" t="n">
-        <v>16.30980481254987</v>
+        <v>16.31132415611261</v>
       </c>
       <c r="O3" t="n">
-        <v>4.038539935737899</v>
+        <v>4.038728036908726</v>
       </c>
       <c r="P3" t="n">
-        <v>321.2714211344117</v>
+        <v>321.2547341272388</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20022,28 +20059,28 @@
         <v>0.1285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09185344915345538</v>
+        <v>0.09385408909686936</v>
       </c>
       <c r="J4" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K4" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04552053555295144</v>
+        <v>0.04740805169994999</v>
       </c>
       <c r="M4" t="n">
-        <v>2.574150266063291</v>
+        <v>2.578261525966499</v>
       </c>
       <c r="N4" t="n">
-        <v>10.41658277181004</v>
+        <v>10.44787035778804</v>
       </c>
       <c r="O4" t="n">
-        <v>3.227473124878043</v>
+        <v>3.23231656212507</v>
       </c>
       <c r="P4" t="n">
-        <v>311.5268828696301</v>
+        <v>311.5062757564336</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20100,28 +20137,28 @@
         <v>0.1609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008819856992375549</v>
+        <v>0.009758670142917427</v>
       </c>
       <c r="J5" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K5" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003973453273249383</v>
+        <v>0.0004881080501841772</v>
       </c>
       <c r="M5" t="n">
-        <v>2.584618354235614</v>
+        <v>2.583050816171733</v>
       </c>
       <c r="N5" t="n">
-        <v>11.52278563701998</v>
+        <v>11.51118014817092</v>
       </c>
       <c r="O5" t="n">
-        <v>3.394522887979985</v>
+        <v>3.392813014029938</v>
       </c>
       <c r="P5" t="n">
-        <v>315.4349239798231</v>
+        <v>315.4252539595242</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20178,28 +20215,28 @@
         <v>0.1333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01085660293649419</v>
+        <v>0.0114094502743029</v>
       </c>
       <c r="J6" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K6" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004464295794311957</v>
+        <v>0.0004951359620267715</v>
       </c>
       <c r="M6" t="n">
-        <v>2.897438446734103</v>
+        <v>2.894836797882779</v>
       </c>
       <c r="N6" t="n">
-        <v>15.53875168716341</v>
+        <v>15.51159509386102</v>
       </c>
       <c r="O6" t="n">
-        <v>3.941922333984196</v>
+        <v>3.938476240103655</v>
       </c>
       <c r="P6" t="n">
-        <v>320.978639713535</v>
+        <v>320.9729452417694</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20237,7 +20274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G499"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38703,6 +38740,43 @@
         </is>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-46.38400092748521,168.01546561308186</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-46.383816460998595,168.01460869278014</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-46.38359379008519,168.01376787887864</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-46.38343717868847,168.01289921699447</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-46.38332946463744,168.01200994049032</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
